--- a/data/trans_orig/IP25A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP25A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6655</t>
+          <t>6832</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>17851</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10196</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22904</t>
+          <t>22340</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23167</t>
+          <t>23586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39118</t>
+          <t>39711</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20922</t>
+          <t>21155</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36039</t>
+          <t>36696</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47936</t>
+          <t>47981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>70599</t>
+          <t>71142</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61631</t>
+          <t>62779</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79623</t>
+          <t>80060</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>63,45%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69264</t>
+          <t>68125</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>87764</t>
+          <t>87055</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>135996</t>
+          <t>135383</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>161431</t>
+          <t>161588</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>61,69%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25787</t>
+          <t>26663</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>13516</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26983</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47657</t>
+          <t>48611</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,56%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6330</t>
+          <t>6404</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16438</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8034</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19681</t>
+          <t>19357</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17044</t>
+          <t>16539</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32533</t>
+          <t>31338</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52386</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71560</t>
+          <t>72261</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49224</t>
+          <t>48817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69163</t>
+          <t>68102</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>106957</t>
+          <t>104407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>133314</t>
+          <t>134297</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>37,73%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69853</t>
+          <t>69602</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89579</t>
+          <t>90686</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>72475</t>
+          <t>73383</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94164</t>
+          <t>94111</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>150831</t>
+          <t>148308</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178170</t>
+          <t>178542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,17%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14738</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28208</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>21301</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>36233</t>
+          <t>37093</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>38680</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60731</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13010</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5128</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15048</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11878</t>
+          <t>11941</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24403</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29789</t>
+          <t>28456</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46088</t>
+          <t>44165</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>34844</t>
+          <t>35378</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51061</t>
+          <t>52637</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69263</t>
+          <t>69141</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>93650</t>
+          <t>91207</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>35,85%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53446</t>
+          <t>54577</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70525</t>
+          <t>71652</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>49758</t>
+          <t>49927</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68724</t>
+          <t>67370</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>109514</t>
+          <t>109967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134741</t>
+          <t>134125</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,72%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10267</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21630</t>
+          <t>20923</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14853</t>
+          <t>15063</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27376</t>
+          <t>27728</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>43935</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,27%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11004</t>
+          <t>10917</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>24962</t>
+          <t>25067</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10194</t>
+          <t>10281</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22174</t>
+          <t>22304</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23664</t>
+          <t>23395</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>42004</t>
+          <t>41923</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>43086</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66767</t>
+          <t>66122</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>52728</t>
+          <t>53075</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72901</t>
+          <t>73768</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103955</t>
+          <t>103768</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>134268</t>
+          <t>133298</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>79918</t>
+          <t>78841</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103646</t>
+          <t>103983</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>40,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71691</t>
+          <t>71521</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93638</t>
+          <t>93046</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>159338</t>
+          <t>158168</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>188850</t>
+          <t>190977</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>22215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39432</t>
+          <t>39797</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13124</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26853</t>
+          <t>26714</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39754</t>
+          <t>39725</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>60320</t>
+          <t>61859</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50301</t>
+          <t>51218</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60353</t>
+          <t>60232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71130</t>
+          <t>75658</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>102545</t>
+          <t>104690</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>166951</t>
+          <t>164920</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>202876</t>
+          <t>201864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172916</t>
+          <t>172001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>211494</t>
+          <t>211871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>351512</t>
+          <t>347600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>402576</t>
+          <t>400946</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>282798</t>
+          <t>285411</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>324170</t>
+          <t>324598</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>280658</t>
+          <t>283827</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>323134</t>
+          <t>325446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>580127</t>
+          <t>576845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>636525</t>
+          <t>636276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>72235</t>
+          <t>73778</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99891</t>
+          <t>101906</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>73415</t>
+          <t>74902</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>101214</t>
+          <t>102460</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>154484</t>
+          <t>154167</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>196713</t>
+          <t>193576</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7356</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19706</t>
+          <t>19441</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13806</t>
+          <t>14109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30619</t>
+          <t>29979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>47604</t>
+          <t>47882</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48452</t>
+          <t>47539</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>64980</t>
+          <t>65000</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>91474</t>
+          <t>91174</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49112</t>
+          <t>48376</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>67429</t>
+          <t>67350</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,26%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>52,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60952</t>
+          <t>60490</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81682</t>
+          <t>80904</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114932</t>
+          <t>115747</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>141857</t>
+          <t>143362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,65%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,2%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17037</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>31873</t>
+          <t>32650</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13412</t>
+          <t>13643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28184</t>
+          <t>27387</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35056</t>
+          <t>34574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55298</t>
+          <t>54178</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6590</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16893</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13291</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27905</t>
+          <t>27211</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22359</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>39268</t>
+          <t>40041</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44735</t>
+          <t>43233</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64263</t>
+          <t>63530</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,54%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41678</t>
+          <t>41585</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61914</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90835</t>
+          <t>90465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119926</t>
+          <t>118120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79135</t>
+          <t>78703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99552</t>
+          <t>100109</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95854</t>
+          <t>95438</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118040</t>
+          <t>118432</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>180818</t>
+          <t>181414</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212672</t>
+          <t>212393</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25349</t>
+          <t>25045</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41789</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16027</t>
+          <t>16352</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>44817</t>
+          <t>45101</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>67470</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7917</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19134</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6159</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15940</t>
+          <t>16786</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16891</t>
+          <t>16815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31127</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>21525</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35718</t>
+          <t>36414</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>32990</t>
+          <t>33629</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51039</t>
+          <t>50792</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>59039</t>
+          <t>59507</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>83051</t>
+          <t>82028</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59713</t>
+          <t>60845</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>79075</t>
+          <t>78639</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>68522</t>
+          <t>68073</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87712</t>
+          <t>86982</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>134749</t>
+          <t>134768</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161301</t>
+          <t>160878</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,33%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14660</t>
+          <t>14712</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27923</t>
+          <t>27298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>27160</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31521</t>
+          <t>31301</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50353</t>
+          <t>49640</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10942</t>
+          <t>10589</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25160</t>
+          <t>25008</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11996</t>
+          <t>12629</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>26753</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26345</t>
+          <t>25450</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45852</t>
+          <t>45827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>45273</t>
+          <t>44378</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66443</t>
+          <t>66938</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45678</t>
+          <t>46743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>66863</t>
+          <t>68268</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>96964</t>
+          <t>98322</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>128460</t>
+          <t>127089</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,61%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75935</t>
+          <t>76215</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>99019</t>
+          <t>100226</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>76234</t>
+          <t>74420</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99140</t>
+          <t>97882</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,67%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>156361</t>
+          <t>157888</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>190845</t>
+          <t>189430</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,1%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19737</t>
+          <t>19394</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35342</t>
+          <t>35451</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23285</t>
+          <t>22828</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39893</t>
+          <t>40292</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>46146</t>
+          <t>46752</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70352</t>
+          <t>71145</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37854</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59229</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>48529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73639</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93248</t>
+          <t>93628</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>124665</t>
+          <t>127224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157589</t>
+          <t>158906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197938</t>
+          <t>195581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>170188</t>
+          <t>170053</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208475</t>
+          <t>208719</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>337908</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>391112</t>
+          <t>390808</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>282950</t>
+          <t>282209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>324299</t>
+          <t>323836</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>321184</t>
+          <t>321945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>365214</t>
+          <t>363940</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>613462</t>
+          <t>617652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>674818</t>
+          <t>676720</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>77980</t>
+          <t>78276</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106742</t>
+          <t>109641</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>176823</t>
+          <t>174682</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>218760</t>
+          <t>220870</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>17330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10887</t>
+          <t>10374</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>23579</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>19200</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36450</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>37905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56036</t>
+          <t>55901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43644</t>
+          <t>43766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62705</t>
+          <t>63949</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86769</t>
+          <t>87211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113636</t>
+          <t>112964</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>44,84%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34278</t>
+          <t>34245</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>52120</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,43%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>37885</t>
+          <t>37964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>56911</t>
+          <t>56877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>78350</t>
+          <t>78750</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>105137</t>
+          <t>105798</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,99%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10951</t>
+          <t>10932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24275</t>
+          <t>23798</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11452</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24825</t>
+          <t>24333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25587</t>
+          <t>25319</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43894</t>
+          <t>43626</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,32%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9204</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20279</t>
+          <t>20364</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5922</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16192</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>17254</t>
+          <t>17161</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>32730</t>
+          <t>32513</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>48778</t>
+          <t>50044</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>68719</t>
+          <t>69524</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62922</t>
+          <t>62822</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84991</t>
+          <t>85143</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>41,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>118199</t>
+          <t>118389</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>146464</t>
+          <t>148097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>38,03%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>66149</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87321</t>
+          <t>86613</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78728</t>
+          <t>77891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>101724</t>
+          <t>100957</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>151981</t>
+          <t>153440</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182384</t>
+          <t>183403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>27754</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>44536</t>
+          <t>44905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>22524</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38287</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54947</t>
+          <t>55074</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>78746</t>
+          <t>78825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,24%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16152</t>
+          <t>16561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30561</t>
+          <t>30680</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11406</t>
+          <t>11253</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25179</t>
+          <t>24852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31434</t>
+          <t>31394</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>50299</t>
+          <t>50258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>35289</t>
+          <t>34438</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52814</t>
+          <t>52889</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39184</t>
+          <t>38161</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>57578</t>
+          <t>57865</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>78161</t>
+          <t>79582</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>102908</t>
+          <t>104718</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,96%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54478</t>
+          <t>52344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71815</t>
+          <t>71113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>67281</t>
+          <t>67858</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>87709</t>
+          <t>89221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>127612</t>
+          <t>127093</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>154508</t>
+          <t>155099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>42,6%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,78%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19764</t>
+          <t>20346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8690</t>
+          <t>8725</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19202</t>
+          <t>20311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20403</t>
+          <t>20268</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>35979</t>
+          <t>35357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>16724</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32207</t>
+          <t>32782</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20387</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36558</t>
+          <t>36683</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>40386</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61769</t>
+          <t>63234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>49047</t>
+          <t>48912</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70764</t>
+          <t>70544</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,75%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,04%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50707</t>
+          <t>51078</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>72239</t>
+          <t>71100</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>106042</t>
+          <t>106609</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>135484</t>
+          <t>136191</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,21%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59556</t>
+          <t>60228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82156</t>
+          <t>80950</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>57384</t>
+          <t>58032</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>79596</t>
+          <t>78697</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>124774</t>
+          <t>123694</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155066</t>
+          <t>155070</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,7 +8905,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>16969</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32618</t>
+          <t>32453</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>16029</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>30496</t>
+          <t>30649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>36955</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57575</t>
+          <t>56670</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>58241</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85717</t>
+          <t>85247</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>58603</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86155</t>
+          <t>86721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>123066</t>
+          <t>124589</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162683</t>
+          <t>160649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>188833</t>
+          <t>191259</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227249</t>
+          <t>228033</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215024</t>
+          <t>215317</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>254255</t>
+          <t>256362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>414361</t>
+          <t>417968</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>471036</t>
+          <t>472738</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>233266</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>272039</t>
+          <t>272241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>263962</t>
+          <t>262142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>305403</t>
+          <t>305591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>509038</t>
+          <t>507451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>566359</t>
+          <t>564289</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>77686</t>
+          <t>77355</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>104903</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70086</t>
+          <t>70337</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>98611</t>
+          <t>97781</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>153922</t>
+          <t>154429</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>194687</t>
+          <t>194649</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>381</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1325</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10059</t>
+          <t>9310</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11348</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>8103</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18414</t>
+          <t>18604</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8048</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22685</t>
+          <t>22779</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18410</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>36395</t>
+          <t>36448</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>43071</t>
+          <t>43761</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>60207</t>
+          <t>60225</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>38,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42206</t>
+          <t>43985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>70092</t>
+          <t>72131</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>92036</t>
+          <t>93095</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>124787</t>
+          <t>125171</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,21%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40316</t>
+          <t>40385</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56832</t>
+          <t>57041</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>50,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51441</t>
+          <t>50077</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83319</t>
+          <t>82155</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>36,64%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>58,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>96404</t>
+          <t>96221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>136620</t>
+          <t>133918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>52,64%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>846</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7454</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>13099</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10588,7 +10588,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4853</t>
+          <t>4658</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16147</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12939</t>
+          <t>13426</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>28629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19327</t>
+          <t>18300</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36874</t>
+          <t>37635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36196</t>
+          <t>35453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60007</t>
+          <t>58900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81422</t>
+          <t>80819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>107022</t>
+          <t>105544</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>103976</t>
+          <t>105099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133185</t>
+          <t>133680</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,19%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>190780</t>
+          <t>190725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232878</t>
+          <t>231362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,44%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61744</t>
+          <t>60093</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>84907</t>
+          <t>84439</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>85612</t>
+          <t>85866</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115083</t>
+          <t>116268</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>45,59%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>154298</t>
+          <t>153783</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194428</t>
+          <t>194244</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,97%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4388</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23223</t>
+          <t>21436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>419</t>
+          <t>404</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6496</t>
+          <t>5954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6198</t>
+          <t>6011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24829</t>
+          <t>24813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>14091</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37071</t>
+          <t>36582</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19049</t>
+          <t>18666</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36611</t>
+          <t>35073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37309</t>
+          <t>37091</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64789</t>
+          <t>65858</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48120</t>
+          <t>48662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97602</t>
+          <t>96041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>83505</t>
+          <t>83166</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111825</t>
+          <t>111130</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138443</t>
+          <t>129277</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>199523</t>
+          <t>198055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,34%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50429</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>121763</t>
+          <t>120069</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45113</t>
+          <t>46348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>73968</t>
+          <t>76031</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,92%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105018</t>
+          <t>106633</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182375</t>
+          <t>191368</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>51,54%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1506</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>8681</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>939</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11726,7 +11726,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13243</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8821</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>20774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14666</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29732</t>
+          <t>30402</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>26293</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46546</t>
+          <t>46317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62317</t>
+          <t>60570</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>83788</t>
+          <t>83647</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,63%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71407</t>
+          <t>71065</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>94098</t>
+          <t>94240</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>139733</t>
+          <t>138339</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>171643</t>
+          <t>170732</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>49,59%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64327</t>
+          <t>64009</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>85838</t>
+          <t>87214</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61150</t>
+          <t>62062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>84457</t>
+          <t>83693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>131708</t>
+          <t>132393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>165257</t>
+          <t>164678</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,74%</t>
+          <t>47,57%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,47 +12275,47 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
+          <t>23920</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>34568</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
           <t>24585</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>34568</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>24886</t>
-        </is>
-      </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>47959</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>54877</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88063</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73126</t>
+          <t>73930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105371</t>
+          <t>106747</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137963</t>
+          <t>139071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181697</t>
+          <t>185336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>254085</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>320838</t>
+          <t>322013</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>327451</t>
+          <t>327457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>384438</t>
+          <t>385562</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>605049</t>
+          <t>607119</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>689743</t>
+          <t>696254</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>242859</t>
+          <t>243566</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>321101</t>
+          <t>326023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>270044</t>
+          <t>269488</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>326274</t>
+          <t>330181</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>527863</t>
+          <t>523578</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>622510</t>
+          <t>620365</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
